--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH860"/>
+  <dimension ref="A1:AH862"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66655,6 +66655,130 @@
       </c>
       <c r="AH860" t="inlineStr"/>
     </row>
+    <row r="861">
+      <c r="A861" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B861" t="n">
+        <v>0.629026595</v>
+      </c>
+      <c r="C861" t="n">
+        <v>0.09801159550000001</v>
+      </c>
+      <c r="D861" t="inlineStr"/>
+      <c r="E861" t="inlineStr"/>
+      <c r="F861" t="inlineStr"/>
+      <c r="G861" t="inlineStr"/>
+      <c r="H861" t="inlineStr"/>
+      <c r="I861" t="n">
+        <v>0.05379677099999999</v>
+      </c>
+      <c r="J861" t="inlineStr"/>
+      <c r="K861" t="n">
+        <v>1559.126557421089</v>
+      </c>
+      <c r="L861" t="inlineStr"/>
+      <c r="M861" t="inlineStr"/>
+      <c r="N861" t="inlineStr"/>
+      <c r="O861" t="n">
+        <v>0.009360439</v>
+      </c>
+      <c r="P861" t="inlineStr"/>
+      <c r="Q861" t="n">
+        <v>1.0488e-06</v>
+      </c>
+      <c r="R861" t="inlineStr"/>
+      <c r="S861" t="inlineStr"/>
+      <c r="T861" t="inlineStr"/>
+      <c r="U861" t="inlineStr"/>
+      <c r="V861" t="inlineStr"/>
+      <c r="W861" t="inlineStr"/>
+      <c r="X861" t="inlineStr"/>
+      <c r="Y861" t="inlineStr"/>
+      <c r="Z861" t="inlineStr"/>
+      <c r="AA861" t="n">
+        <v>0.8384278614544</v>
+      </c>
+      <c r="AB861" t="n">
+        <v>242.925405408</v>
+      </c>
+      <c r="AC861" t="n">
+        <v>8.999358638272801</v>
+      </c>
+      <c r="AD861" t="n">
+        <v>0.153143965</v>
+      </c>
+      <c r="AE861" t="n">
+        <v>1812.861954809116</v>
+      </c>
+      <c r="AF861" t="inlineStr"/>
+      <c r="AG861" t="n">
+        <v>0.028865066</v>
+      </c>
+      <c r="AH861" t="inlineStr"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B862" t="n">
+        <v>0.6293164</v>
+      </c>
+      <c r="C862" t="n">
+        <v>0.09773242750000001</v>
+      </c>
+      <c r="D862" t="inlineStr"/>
+      <c r="E862" t="inlineStr"/>
+      <c r="F862" t="inlineStr"/>
+      <c r="G862" t="inlineStr"/>
+      <c r="H862" t="inlineStr"/>
+      <c r="I862" t="n">
+        <v>0.05405376899999999</v>
+      </c>
+      <c r="J862" t="inlineStr"/>
+      <c r="K862" t="n">
+        <v>1554.929088376282</v>
+      </c>
+      <c r="L862" t="inlineStr"/>
+      <c r="M862" t="inlineStr"/>
+      <c r="N862" t="inlineStr"/>
+      <c r="O862" t="n">
+        <v>0.009424689999999999</v>
+      </c>
+      <c r="P862" t="inlineStr"/>
+      <c r="Q862" t="n">
+        <v>1.0464e-06</v>
+      </c>
+      <c r="R862" t="inlineStr"/>
+      <c r="S862" t="inlineStr"/>
+      <c r="T862" t="inlineStr"/>
+      <c r="U862" t="inlineStr"/>
+      <c r="V862" t="inlineStr"/>
+      <c r="W862" t="inlineStr"/>
+      <c r="X862" t="inlineStr"/>
+      <c r="Y862" t="inlineStr"/>
+      <c r="Z862" t="inlineStr"/>
+      <c r="AA862" t="n">
+        <v>0.8384530110207999</v>
+      </c>
+      <c r="AB862" t="n">
+        <v>233.26787441</v>
+      </c>
+      <c r="AC862" t="n">
+        <v>8.8316687257584</v>
+      </c>
+      <c r="AD862" t="n">
+        <v>0.15145806</v>
+      </c>
+      <c r="AE862" t="n">
+        <v>1798.837418971961</v>
+      </c>
+      <c r="AF862" t="inlineStr"/>
+      <c r="AG862" t="n">
+        <v>0.028348056</v>
+      </c>
+      <c r="AH862" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH862"/>
+  <dimension ref="A1:AH863"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66213,7 +66213,7 @@
         <v>0.11637301</v>
       </c>
       <c r="AE853" t="n">
-        <v>1816.980927733444</v>
+        <v>1816.980927733443</v>
       </c>
       <c r="AF853" t="inlineStr"/>
       <c r="AG853" t="n">
@@ -66779,6 +66779,68 @@
       </c>
       <c r="AH862" t="inlineStr"/>
     </row>
+    <row r="863">
+      <c r="A863" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B863" t="n">
+        <v>0.6220750745</v>
+      </c>
+      <c r="C863" t="n">
+        <v>0.09773460850000001</v>
+      </c>
+      <c r="D863" t="inlineStr"/>
+      <c r="E863" t="inlineStr"/>
+      <c r="F863" t="inlineStr"/>
+      <c r="G863" t="inlineStr"/>
+      <c r="H863" t="inlineStr"/>
+      <c r="I863" t="n">
+        <v>0.052680159</v>
+      </c>
+      <c r="J863" t="inlineStr"/>
+      <c r="K863" t="n">
+        <v>1565.189568263588</v>
+      </c>
+      <c r="L863" t="inlineStr"/>
+      <c r="M863" t="inlineStr"/>
+      <c r="N863" t="inlineStr"/>
+      <c r="O863" t="n">
+        <v>0.009243916</v>
+      </c>
+      <c r="P863" t="inlineStr"/>
+      <c r="Q863" t="n">
+        <v>1.0104e-06</v>
+      </c>
+      <c r="R863" t="inlineStr"/>
+      <c r="S863" t="inlineStr"/>
+      <c r="T863" t="inlineStr"/>
+      <c r="U863" t="inlineStr"/>
+      <c r="V863" t="inlineStr"/>
+      <c r="W863" t="inlineStr"/>
+      <c r="X863" t="inlineStr"/>
+      <c r="Y863" t="inlineStr"/>
+      <c r="Z863" t="inlineStr"/>
+      <c r="AA863" t="n">
+        <v>0.8386961234960001</v>
+      </c>
+      <c r="AB863" t="n">
+        <v>217.993927789</v>
+      </c>
+      <c r="AC863" t="n">
+        <v>8.38449562572</v>
+      </c>
+      <c r="AD863" t="n">
+        <v>0.14143376</v>
+      </c>
+      <c r="AE863" t="n">
+        <v>1793.357393078204</v>
+      </c>
+      <c r="AF863" t="inlineStr"/>
+      <c r="AG863" t="n">
+        <v>0.027536748</v>
+      </c>
+      <c r="AH863" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH863"/>
+  <dimension ref="A1:AH867"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66841,6 +66841,254 @@
       </c>
       <c r="AH863" t="inlineStr"/>
     </row>
+    <row r="864">
+      <c r="A864" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B864" t="n">
+        <v>0.623294267</v>
+      </c>
+      <c r="C864" t="n">
+        <v>0.097344573</v>
+      </c>
+      <c r="D864" t="inlineStr"/>
+      <c r="E864" t="inlineStr"/>
+      <c r="F864" t="inlineStr"/>
+      <c r="G864" t="inlineStr"/>
+      <c r="H864" t="inlineStr"/>
+      <c r="I864" t="n">
+        <v>0.052795365</v>
+      </c>
+      <c r="J864" t="inlineStr"/>
+      <c r="K864" t="n">
+        <v>1559.592942870512</v>
+      </c>
+      <c r="L864" t="inlineStr"/>
+      <c r="M864" t="inlineStr"/>
+      <c r="N864" t="inlineStr"/>
+      <c r="O864" t="n">
+        <v>0.009179785999999999</v>
+      </c>
+      <c r="P864" t="inlineStr"/>
+      <c r="Q864" t="n">
+        <v>1.0224e-06</v>
+      </c>
+      <c r="R864" t="inlineStr"/>
+      <c r="S864" t="inlineStr"/>
+      <c r="T864" t="inlineStr"/>
+      <c r="U864" t="inlineStr"/>
+      <c r="V864" t="inlineStr"/>
+      <c r="W864" t="inlineStr"/>
+      <c r="X864" t="inlineStr"/>
+      <c r="Y864" t="inlineStr"/>
+      <c r="Z864" t="inlineStr"/>
+      <c r="AA864" t="n">
+        <v>0.8386542075519999</v>
+      </c>
+      <c r="AB864" t="n">
+        <v>208.280555924</v>
+      </c>
+      <c r="AC864" t="n">
+        <v>8.2168057132056</v>
+      </c>
+      <c r="AD864" t="n">
+        <v>0.140203505</v>
+      </c>
+      <c r="AE864" t="n">
+        <v>1777.878355524669</v>
+      </c>
+      <c r="AF864" t="inlineStr"/>
+      <c r="AG864" t="n">
+        <v>0.026578291</v>
+      </c>
+      <c r="AH864" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B865" t="n">
+        <v>0.62299582</v>
+      </c>
+      <c r="C865" t="n">
+        <v>0.09763646350000002</v>
+      </c>
+      <c r="D865" t="inlineStr"/>
+      <c r="E865" t="inlineStr"/>
+      <c r="F865" t="inlineStr"/>
+      <c r="G865" t="inlineStr"/>
+      <c r="H865" t="inlineStr"/>
+      <c r="I865" t="n">
+        <v>0.052338972</v>
+      </c>
+      <c r="J865" t="inlineStr"/>
+      <c r="K865" t="n">
+        <v>1573.584506353202</v>
+      </c>
+      <c r="L865" t="inlineStr"/>
+      <c r="M865" t="inlineStr"/>
+      <c r="N865" t="inlineStr"/>
+      <c r="O865" t="n">
+        <v>0.009308166999999999</v>
+      </c>
+      <c r="P865" t="inlineStr"/>
+      <c r="Q865" t="n">
+        <v>1.0272e-06</v>
+      </c>
+      <c r="R865" t="inlineStr"/>
+      <c r="S865" t="inlineStr"/>
+      <c r="T865" t="inlineStr"/>
+      <c r="U865" t="inlineStr"/>
+      <c r="V865" t="inlineStr"/>
+      <c r="W865" t="inlineStr"/>
+      <c r="X865" t="inlineStr"/>
+      <c r="Y865" t="inlineStr"/>
+      <c r="Z865" t="inlineStr"/>
+      <c r="AA865" t="n">
+        <v>0.8388386377056001</v>
+      </c>
+      <c r="AB865" t="n">
+        <v>211.3738460565</v>
+      </c>
+      <c r="AC865" t="n">
+        <v>8.2727023507104</v>
+      </c>
+      <c r="AD865" t="n">
+        <v>0.13952003</v>
+      </c>
+      <c r="AE865" t="n">
+        <v>1795.018439202817</v>
+      </c>
+      <c r="AF865" t="inlineStr"/>
+      <c r="AG865" t="n">
+        <v>0.026745325</v>
+      </c>
+      <c r="AH865" t="inlineStr"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B866" t="n">
+        <v>0.6323563725</v>
+      </c>
+      <c r="C866" t="n">
+        <v>0.09837836700000001</v>
+      </c>
+      <c r="D866" t="inlineStr"/>
+      <c r="E866" t="inlineStr"/>
+      <c r="F866" t="inlineStr"/>
+      <c r="G866" t="inlineStr"/>
+      <c r="H866" t="inlineStr"/>
+      <c r="I866" t="n">
+        <v>0.05246747099999999</v>
+      </c>
+      <c r="J866" t="inlineStr"/>
+      <c r="K866" t="n">
+        <v>1561.458484668204</v>
+      </c>
+      <c r="L866" t="inlineStr"/>
+      <c r="M866" t="inlineStr"/>
+      <c r="N866" t="inlineStr"/>
+      <c r="O866" t="n">
+        <v>0.009338174999999999</v>
+      </c>
+      <c r="P866" t="inlineStr"/>
+      <c r="Q866" t="n">
+        <v>1.0632e-06</v>
+      </c>
+      <c r="R866" t="inlineStr"/>
+      <c r="S866" t="inlineStr"/>
+      <c r="T866" t="inlineStr"/>
+      <c r="U866" t="inlineStr"/>
+      <c r="V866" t="inlineStr"/>
+      <c r="W866" t="inlineStr"/>
+      <c r="X866" t="inlineStr"/>
+      <c r="Y866" t="inlineStr"/>
+      <c r="Z866" t="inlineStr"/>
+      <c r="AA866" t="n">
+        <v>0.8385787588528</v>
+      </c>
+      <c r="AB866" t="n">
+        <v>196.260074554</v>
+      </c>
+      <c r="AC866" t="n">
+        <v>8.2540701382088</v>
+      </c>
+      <c r="AD866" t="n">
+        <v>0.140932545</v>
+      </c>
+      <c r="AE866" t="n">
+        <v>1767.771773436965</v>
+      </c>
+      <c r="AF866" t="inlineStr"/>
+      <c r="AG866" t="n">
+        <v>0.027091324</v>
+      </c>
+      <c r="AH866" t="inlineStr"/>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B867" t="n">
+        <v>0.6296591745</v>
+      </c>
+      <c r="C867" t="n">
+        <v>0.09700324650000001</v>
+      </c>
+      <c r="D867" t="inlineStr"/>
+      <c r="E867" t="inlineStr"/>
+      <c r="F867" t="inlineStr"/>
+      <c r="G867" t="inlineStr"/>
+      <c r="H867" t="inlineStr"/>
+      <c r="I867" t="n">
+        <v>0.052573815</v>
+      </c>
+      <c r="J867" t="inlineStr"/>
+      <c r="K867" t="n">
+        <v>1560.992099218781</v>
+      </c>
+      <c r="L867" t="inlineStr"/>
+      <c r="M867" t="inlineStr"/>
+      <c r="N867" t="inlineStr"/>
+      <c r="O867" t="n">
+        <v>0.009295824999999999</v>
+      </c>
+      <c r="P867" t="inlineStr"/>
+      <c r="Q867" t="n">
+        <v>1.02e-06</v>
+      </c>
+      <c r="R867" t="inlineStr"/>
+      <c r="S867" t="inlineStr"/>
+      <c r="T867" t="inlineStr"/>
+      <c r="U867" t="inlineStr"/>
+      <c r="V867" t="inlineStr"/>
+      <c r="W867" t="inlineStr"/>
+      <c r="X867" t="inlineStr"/>
+      <c r="Y867" t="inlineStr"/>
+      <c r="Z867" t="inlineStr"/>
+      <c r="AA867" t="n">
+        <v>0.8384781605871999</v>
+      </c>
+      <c r="AB867" t="n">
+        <v>191.252030482</v>
+      </c>
+      <c r="AC867" t="n">
+        <v>8.3285989882152</v>
+      </c>
+      <c r="AD867" t="n">
+        <v>0.14198054</v>
+      </c>
+      <c r="AE867" t="n">
+        <v>1762.369515723583</v>
+      </c>
+      <c r="AF867" t="inlineStr"/>
+      <c r="AG867" t="n">
+        <v>0.027795253</v>
+      </c>
+      <c r="AH867" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -66213,7 +66213,7 @@
         <v>0.11637301</v>
       </c>
       <c r="AE853" t="n">
-        <v>1816.980927733443</v>
+        <v>1816.980927733444</v>
       </c>
       <c r="AF853" t="inlineStr"/>
       <c r="AG853" t="n">
@@ -66895,7 +66895,7 @@
         <v>0.140203505</v>
       </c>
       <c r="AE864" t="n">
-        <v>1777.878355524669</v>
+        <v>1777.87835552467</v>
       </c>
       <c r="AF864" t="inlineStr"/>
       <c r="AG864" t="n">

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH867"/>
+  <dimension ref="A1:AH869"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66957,7 +66957,7 @@
         <v>0.13952003</v>
       </c>
       <c r="AE865" t="n">
-        <v>1795.018439202817</v>
+        <v>1795.018439202818</v>
       </c>
       <c r="AF865" t="inlineStr"/>
       <c r="AG865" t="n">
@@ -67089,6 +67089,130 @@
       </c>
       <c r="AH867" t="inlineStr"/>
     </row>
+    <row r="868">
+      <c r="A868" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B868" t="n">
+        <v>125.9471803024</v>
+      </c>
+      <c r="C868" t="n">
+        <v>0.09768081050000001</v>
+      </c>
+      <c r="D868" t="inlineStr"/>
+      <c r="E868" t="inlineStr"/>
+      <c r="F868" t="inlineStr"/>
+      <c r="G868" t="inlineStr"/>
+      <c r="H868" t="inlineStr"/>
+      <c r="I868" t="n">
+        <v>0.053003622</v>
+      </c>
+      <c r="J868" t="inlineStr"/>
+      <c r="K868" t="n">
+        <v>1564.256797364742</v>
+      </c>
+      <c r="L868" t="inlineStr"/>
+      <c r="M868" t="inlineStr"/>
+      <c r="N868" t="inlineStr"/>
+      <c r="O868" t="n">
+        <v>15.6575506976</v>
+      </c>
+      <c r="P868" t="inlineStr"/>
+      <c r="Q868" t="n">
+        <v>1.0344e-06</v>
+      </c>
+      <c r="R868" t="inlineStr"/>
+      <c r="S868" t="inlineStr"/>
+      <c r="T868" t="inlineStr"/>
+      <c r="U868" t="inlineStr"/>
+      <c r="V868" t="inlineStr"/>
+      <c r="W868" t="inlineStr"/>
+      <c r="X868" t="inlineStr"/>
+      <c r="Y868" t="inlineStr"/>
+      <c r="Z868" t="inlineStr"/>
+      <c r="AA868" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB868" t="n">
+        <v>36.478765194</v>
+      </c>
+      <c r="AC868" t="n">
+        <v>8.496288900729599</v>
+      </c>
+      <c r="AD868" t="n">
+        <v>0.145671305</v>
+      </c>
+      <c r="AE868" t="n">
+        <v>1766.826949524871</v>
+      </c>
+      <c r="AF868" t="inlineStr"/>
+      <c r="AG868" t="n">
+        <v>15.6940102935</v>
+      </c>
+      <c r="AH868" t="inlineStr"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B869" t="n">
+        <v>128.5870412</v>
+      </c>
+      <c r="C869" t="n">
+        <v>0.09912426900000001</v>
+      </c>
+      <c r="D869" t="inlineStr"/>
+      <c r="E869" t="inlineStr"/>
+      <c r="F869" t="inlineStr"/>
+      <c r="G869" t="inlineStr"/>
+      <c r="H869" t="inlineStr"/>
+      <c r="I869" t="n">
+        <v>0.05388096</v>
+      </c>
+      <c r="J869" t="inlineStr"/>
+      <c r="K869" t="n">
+        <v>1565.655953713011</v>
+      </c>
+      <c r="L869" t="inlineStr"/>
+      <c r="M869" t="inlineStr"/>
+      <c r="N869" t="inlineStr"/>
+      <c r="O869" t="n">
+        <v>15.8276809061</v>
+      </c>
+      <c r="P869" t="inlineStr"/>
+      <c r="Q869" t="n">
+        <v>1.0584e-06</v>
+      </c>
+      <c r="R869" t="inlineStr"/>
+      <c r="S869" t="inlineStr"/>
+      <c r="T869" t="inlineStr"/>
+      <c r="U869" t="inlineStr"/>
+      <c r="V869" t="inlineStr"/>
+      <c r="W869" t="inlineStr"/>
+      <c r="X869" t="inlineStr"/>
+      <c r="Y869" t="inlineStr"/>
+      <c r="Z869" t="inlineStr"/>
+      <c r="AA869" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB869" t="n">
+        <v>37.79826817049999</v>
+      </c>
+      <c r="AC869" t="n">
+        <v>8.5335533257328</v>
+      </c>
+      <c r="AD869" t="n">
+        <v>0.145306785</v>
+      </c>
+      <c r="AE869" t="n">
+        <v>1772.486363492744</v>
+      </c>
+      <c r="AF869" t="inlineStr"/>
+      <c r="AG869" t="n">
+        <v>15.785553105</v>
+      </c>
+      <c r="AH869" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH869"/>
+  <dimension ref="A1:AH870"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66213,7 +66213,7 @@
         <v>0.11637301</v>
       </c>
       <c r="AE853" t="n">
-        <v>1816.980927733444</v>
+        <v>1816.980927733443</v>
       </c>
       <c r="AF853" t="inlineStr"/>
       <c r="AG853" t="n">
@@ -66895,7 +66895,7 @@
         <v>0.140203505</v>
       </c>
       <c r="AE864" t="n">
-        <v>1777.87835552467</v>
+        <v>1777.878355524669</v>
       </c>
       <c r="AF864" t="inlineStr"/>
       <c r="AG864" t="n">
@@ -67213,6 +67213,68 @@
       </c>
       <c r="AH869" t="inlineStr"/>
     </row>
+    <row r="870">
+      <c r="A870" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B870" t="n">
+        <v>127.4529994948</v>
+      </c>
+      <c r="C870" t="n">
+        <v>0.09850777300000001</v>
+      </c>
+      <c r="D870" t="inlineStr"/>
+      <c r="E870" t="inlineStr"/>
+      <c r="F870" t="inlineStr"/>
+      <c r="G870" t="inlineStr"/>
+      <c r="H870" t="inlineStr"/>
+      <c r="I870" t="n">
+        <v>0.053517618</v>
+      </c>
+      <c r="J870" t="inlineStr"/>
+      <c r="K870" t="n">
+        <v>1567.521495510703</v>
+      </c>
+      <c r="L870" t="inlineStr"/>
+      <c r="M870" t="inlineStr"/>
+      <c r="N870" t="inlineStr"/>
+      <c r="O870" t="n">
+        <v>15.6485964761</v>
+      </c>
+      <c r="P870" t="inlineStr"/>
+      <c r="Q870" t="n">
+        <v>1.0536e-06</v>
+      </c>
+      <c r="R870" t="inlineStr"/>
+      <c r="S870" t="inlineStr"/>
+      <c r="T870" t="inlineStr"/>
+      <c r="U870" t="inlineStr"/>
+      <c r="V870" t="inlineStr"/>
+      <c r="W870" t="inlineStr"/>
+      <c r="X870" t="inlineStr"/>
+      <c r="Y870" t="inlineStr"/>
+      <c r="Z870" t="inlineStr"/>
+      <c r="AA870" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB870" t="n">
+        <v>37.387128819</v>
+      </c>
+      <c r="AC870" t="n">
+        <v>8.496288900729599</v>
+      </c>
+      <c r="AD870" t="n">
+        <v>0.14434992</v>
+      </c>
+      <c r="AE870" t="n">
+        <v>1772.454473580932</v>
+      </c>
+      <c r="AF870" t="inlineStr"/>
+      <c r="AG870" t="n">
+        <v>15.651588015</v>
+      </c>
+      <c r="AH870" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH870"/>
+  <dimension ref="A1:AH871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66957,7 +66957,7 @@
         <v>0.13952003</v>
       </c>
       <c r="AE865" t="n">
-        <v>1795.018439202818</v>
+        <v>1795.018439202817</v>
       </c>
       <c r="AF865" t="inlineStr"/>
       <c r="AG865" t="n">
@@ -67275,6 +67275,68 @@
       </c>
       <c r="AH870" t="inlineStr"/>
     </row>
+    <row r="871">
+      <c r="A871" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B871" t="n">
+        <v>127.1306179772</v>
+      </c>
+      <c r="C871" t="n">
+        <v>0.0980537615</v>
+      </c>
+      <c r="D871" t="inlineStr"/>
+      <c r="E871" t="inlineStr"/>
+      <c r="F871" t="inlineStr"/>
+      <c r="G871" t="inlineStr"/>
+      <c r="H871" t="inlineStr"/>
+      <c r="I871" t="n">
+        <v>0.05348660099999999</v>
+      </c>
+      <c r="J871" t="inlineStr"/>
+      <c r="K871" t="n">
+        <v>1564.723182814165</v>
+      </c>
+      <c r="L871" t="inlineStr"/>
+      <c r="M871" t="inlineStr"/>
+      <c r="N871" t="inlineStr"/>
+      <c r="O871" t="n">
+        <v>0.6572510149999999</v>
+      </c>
+      <c r="P871" t="inlineStr"/>
+      <c r="Q871" t="n">
+        <v>1.0272e-06</v>
+      </c>
+      <c r="R871" t="inlineStr"/>
+      <c r="S871" t="inlineStr"/>
+      <c r="T871" t="inlineStr"/>
+      <c r="U871" t="inlineStr"/>
+      <c r="V871" t="inlineStr"/>
+      <c r="W871" t="inlineStr"/>
+      <c r="X871" t="inlineStr"/>
+      <c r="Y871" t="inlineStr"/>
+      <c r="Z871" t="inlineStr"/>
+      <c r="AA871" t="n">
+        <v>0.1734334686</v>
+      </c>
+      <c r="AB871" t="n">
+        <v>68.26368917250001</v>
+      </c>
+      <c r="AC871" t="n">
+        <v>8.477656688228</v>
+      </c>
+      <c r="AD871" t="n">
+        <v>0.14207167</v>
+      </c>
+      <c r="AE871" t="n">
+        <v>1769.738426793893</v>
+      </c>
+      <c r="AF871" t="inlineStr"/>
+      <c r="AG871" t="n">
+        <v>0.0189825985</v>
+      </c>
+      <c r="AH871" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH871"/>
+  <dimension ref="A1:AH872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66213,7 +66213,7 @@
         <v>0.11637301</v>
       </c>
       <c r="AE853" t="n">
-        <v>1816.980927733444</v>
+        <v>1816.980927733443</v>
       </c>
       <c r="AF853" t="inlineStr"/>
       <c r="AG853" t="n">
@@ -66957,7 +66957,7 @@
         <v>0.13952003</v>
       </c>
       <c r="AE865" t="n">
-        <v>1795.018439202817</v>
+        <v>1795.018439202818</v>
       </c>
       <c r="AF865" t="inlineStr"/>
       <c r="AG865" t="n">
@@ -67337,6 +67337,68 @@
       </c>
       <c r="AH871" t="inlineStr"/>
     </row>
+    <row r="872">
+      <c r="A872" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B872" t="n">
+        <v>123.8195425324</v>
+      </c>
+      <c r="C872" t="n">
+        <v>0.09356998900000001</v>
+      </c>
+      <c r="D872" t="inlineStr"/>
+      <c r="E872" t="inlineStr"/>
+      <c r="F872" t="inlineStr"/>
+      <c r="G872" t="inlineStr"/>
+      <c r="H872" t="inlineStr"/>
+      <c r="I872" t="n">
+        <v>0.05153253</v>
+      </c>
+      <c r="J872" t="inlineStr"/>
+      <c r="K872" t="n">
+        <v>1564.256797364742</v>
+      </c>
+      <c r="L872" t="inlineStr"/>
+      <c r="M872" t="inlineStr"/>
+      <c r="N872" t="inlineStr"/>
+      <c r="O872" t="n">
+        <v>0.6513066665</v>
+      </c>
+      <c r="P872" t="inlineStr"/>
+      <c r="Q872" t="n">
+        <v>9.839999999999998e-07</v>
+      </c>
+      <c r="R872" t="inlineStr"/>
+      <c r="S872" t="inlineStr"/>
+      <c r="T872" t="inlineStr"/>
+      <c r="U872" t="inlineStr"/>
+      <c r="V872" t="inlineStr"/>
+      <c r="W872" t="inlineStr"/>
+      <c r="X872" t="inlineStr"/>
+      <c r="Y872" t="inlineStr"/>
+      <c r="Z872" t="inlineStr"/>
+      <c r="AA872" t="n">
+        <v>0.1734802947</v>
+      </c>
+      <c r="AB872" t="n">
+        <v>66.332136207</v>
+      </c>
+      <c r="AC872" t="n">
+        <v>8.3285989882152</v>
+      </c>
+      <c r="AD872" t="n">
+        <v>0.136831695</v>
+      </c>
+      <c r="AE872" t="n">
+        <v>1763.861987418057</v>
+      </c>
+      <c r="AF872" t="inlineStr"/>
+      <c r="AG872" t="n">
+        <v>0.0181901665</v>
+      </c>
+      <c r="AH872" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH872"/>
+  <dimension ref="A1:AH873"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66895,7 +66895,7 @@
         <v>0.140203505</v>
       </c>
       <c r="AE864" t="n">
-        <v>1777.87835552467</v>
+        <v>1777.878355524669</v>
       </c>
       <c r="AF864" t="inlineStr"/>
       <c r="AG864" t="n">
@@ -67399,6 +67399,68 @@
       </c>
       <c r="AH872" t="inlineStr"/>
     </row>
+    <row r="873">
+      <c r="A873" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B873" t="n">
+        <v>121.490382878</v>
+      </c>
+      <c r="C873" t="n">
+        <v>0.08995898000000001</v>
+      </c>
+      <c r="D873" t="inlineStr"/>
+      <c r="E873" t="inlineStr"/>
+      <c r="F873" t="inlineStr"/>
+      <c r="G873" t="inlineStr"/>
+      <c r="H873" t="inlineStr"/>
+      <c r="I873" t="n">
+        <v>0.048572622</v>
+      </c>
+      <c r="J873" t="inlineStr"/>
+      <c r="K873" t="n">
+        <v>1552.130775679744</v>
+      </c>
+      <c r="L873" t="inlineStr"/>
+      <c r="M873" t="inlineStr"/>
+      <c r="N873" t="inlineStr"/>
+      <c r="O873" t="n">
+        <v>0.6206405736</v>
+      </c>
+      <c r="P873" t="inlineStr"/>
+      <c r="Q873" t="n">
+        <v>9.191999999999999e-07</v>
+      </c>
+      <c r="R873" t="inlineStr"/>
+      <c r="S873" t="inlineStr"/>
+      <c r="T873" t="inlineStr"/>
+      <c r="U873" t="inlineStr"/>
+      <c r="V873" t="inlineStr"/>
+      <c r="W873" t="inlineStr"/>
+      <c r="X873" t="inlineStr"/>
+      <c r="Y873" t="inlineStr"/>
+      <c r="Z873" t="inlineStr"/>
+      <c r="AA873" t="n">
+        <v>0.1735409952</v>
+      </c>
+      <c r="AB873" t="n">
+        <v>59.291233543</v>
+      </c>
+      <c r="AC873" t="n">
+        <v>8.030483588189599</v>
+      </c>
+      <c r="AD873" t="n">
+        <v>0.123526715</v>
+      </c>
+      <c r="AE873" t="n">
+        <v>1742.016494967933</v>
+      </c>
+      <c r="AF873" t="inlineStr"/>
+      <c r="AG873" t="n">
+        <v>0.017378474</v>
+      </c>
+      <c r="AH873" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH873"/>
+  <dimension ref="A1:AH875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66213,7 +66213,7 @@
         <v>0.11637301</v>
       </c>
       <c r="AE853" t="n">
-        <v>1816.980927733443</v>
+        <v>1816.980927733444</v>
       </c>
       <c r="AF853" t="inlineStr"/>
       <c r="AG853" t="n">
@@ -66895,7 +66895,7 @@
         <v>0.140203505</v>
       </c>
       <c r="AE864" t="n">
-        <v>1777.878355524669</v>
+        <v>1777.87835552467</v>
       </c>
       <c r="AF864" t="inlineStr"/>
       <c r="AG864" t="n">
@@ -67453,13 +67453,137 @@
         <v>0.123526715</v>
       </c>
       <c r="AE873" t="n">
-        <v>1742.016494967933</v>
+        <v>1742.016494967934</v>
       </c>
       <c r="AF873" t="inlineStr"/>
       <c r="AG873" t="n">
         <v>0.017378474</v>
       </c>
       <c r="AH873" t="inlineStr"/>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B874" t="n">
+        <v>122.799732722</v>
+      </c>
+      <c r="C874" t="n">
+        <v>0.09042789499999999</v>
+      </c>
+      <c r="D874" t="inlineStr"/>
+      <c r="E874" t="inlineStr"/>
+      <c r="F874" t="inlineStr"/>
+      <c r="G874" t="inlineStr"/>
+      <c r="H874" t="inlineStr"/>
+      <c r="I874" t="n">
+        <v>0.04835550299999999</v>
+      </c>
+      <c r="J874" t="inlineStr"/>
+      <c r="K874" t="n">
+        <v>1547.933306634937</v>
+      </c>
+      <c r="L874" t="inlineStr"/>
+      <c r="M874" t="inlineStr"/>
+      <c r="N874" t="inlineStr"/>
+      <c r="O874" t="n">
+        <v>0.6259019544000001</v>
+      </c>
+      <c r="P874" t="inlineStr"/>
+      <c r="Q874" t="n">
+        <v>9.504e-07</v>
+      </c>
+      <c r="R874" t="inlineStr"/>
+      <c r="S874" t="inlineStr"/>
+      <c r="T874" t="inlineStr"/>
+      <c r="U874" t="inlineStr"/>
+      <c r="V874" t="inlineStr"/>
+      <c r="W874" t="inlineStr"/>
+      <c r="X874" t="inlineStr"/>
+      <c r="Y874" t="inlineStr"/>
+      <c r="Z874" t="inlineStr"/>
+      <c r="AA874" t="n">
+        <v>0.173568744</v>
+      </c>
+      <c r="AB874" t="n">
+        <v>60.23228494899999</v>
+      </c>
+      <c r="AC874" t="n">
+        <v>8.309966775713601</v>
+      </c>
+      <c r="AD874" t="n">
+        <v>0.125987225</v>
+      </c>
+      <c r="AE874" t="n">
+        <v>1740.35699712395</v>
+      </c>
+      <c r="AF874" t="inlineStr"/>
+      <c r="AG874" t="n">
+        <v>0.0174637705</v>
+      </c>
+      <c r="AH874" t="inlineStr"/>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B875" t="n">
+        <v>123.3240224944</v>
+      </c>
+      <c r="C875" t="n">
+        <v>0.09111200200000001</v>
+      </c>
+      <c r="D875" t="inlineStr"/>
+      <c r="E875" t="inlineStr"/>
+      <c r="F875" t="inlineStr"/>
+      <c r="G875" t="inlineStr"/>
+      <c r="H875" t="inlineStr"/>
+      <c r="I875" t="n">
+        <v>0.048780879</v>
+      </c>
+      <c r="J875" t="inlineStr"/>
+      <c r="K875" t="n">
+        <v>1542.803066691284</v>
+      </c>
+      <c r="L875" t="inlineStr"/>
+      <c r="M875" t="inlineStr"/>
+      <c r="N875" t="inlineStr"/>
+      <c r="O875" t="n">
+        <v>0.6325039754999999</v>
+      </c>
+      <c r="P875" t="inlineStr"/>
+      <c r="Q875" t="n">
+        <v>9.696e-07</v>
+      </c>
+      <c r="R875" t="inlineStr"/>
+      <c r="S875" t="inlineStr"/>
+      <c r="T875" t="inlineStr"/>
+      <c r="U875" t="inlineStr"/>
+      <c r="V875" t="inlineStr"/>
+      <c r="W875" t="inlineStr"/>
+      <c r="X875" t="inlineStr"/>
+      <c r="Y875" t="inlineStr"/>
+      <c r="Z875" t="inlineStr"/>
+      <c r="AA875" t="n">
+        <v>0.1735739469</v>
+      </c>
+      <c r="AB875" t="n">
+        <v>61.037473307</v>
+      </c>
+      <c r="AC875" t="n">
+        <v>8.477656688228</v>
+      </c>
+      <c r="AD875" t="n">
+        <v>0.127582</v>
+      </c>
+      <c r="AE875" t="n">
+        <v>1736.733388056912</v>
+      </c>
+      <c r="AF875" t="inlineStr"/>
+      <c r="AG875" t="n">
+        <v>0.017615103</v>
+      </c>
+      <c r="AH875" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH875"/>
+  <dimension ref="A1:AH876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66895,7 +66895,7 @@
         <v>0.140203505</v>
       </c>
       <c r="AE864" t="n">
-        <v>1777.87835552467</v>
+        <v>1777.878355524669</v>
       </c>
       <c r="AF864" t="inlineStr"/>
       <c r="AG864" t="n">
@@ -67453,7 +67453,7 @@
         <v>0.123526715</v>
       </c>
       <c r="AE873" t="n">
-        <v>1742.016494967934</v>
+        <v>1742.016494967933</v>
       </c>
       <c r="AF873" t="inlineStr"/>
       <c r="AG873" t="n">
@@ -67585,6 +67585,68 @@
       </c>
       <c r="AH875" t="inlineStr"/>
     </row>
+    <row r="876">
+      <c r="A876" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B876" t="n">
+        <v>124.4902072448</v>
+      </c>
+      <c r="C876" t="n">
+        <v>0.092217769</v>
+      </c>
+      <c r="D876" t="inlineStr"/>
+      <c r="E876" t="inlineStr"/>
+      <c r="F876" t="inlineStr"/>
+      <c r="G876" t="inlineStr"/>
+      <c r="H876" t="inlineStr"/>
+      <c r="I876" t="n">
+        <v>0.04933918499999999</v>
+      </c>
+      <c r="J876" t="inlineStr"/>
+      <c r="K876" t="n">
+        <v>1540.004753994746</v>
+      </c>
+      <c r="L876" t="inlineStr"/>
+      <c r="M876" t="inlineStr"/>
+      <c r="N876" t="inlineStr"/>
+      <c r="O876" t="n">
+        <v>0.6359525408</v>
+      </c>
+      <c r="P876" t="inlineStr"/>
+      <c r="Q876" t="n">
+        <v>1.0128e-06</v>
+      </c>
+      <c r="R876" t="inlineStr"/>
+      <c r="S876" t="inlineStr"/>
+      <c r="T876" t="inlineStr"/>
+      <c r="U876" t="inlineStr"/>
+      <c r="V876" t="inlineStr"/>
+      <c r="W876" t="inlineStr"/>
+      <c r="X876" t="inlineStr"/>
+      <c r="Y876" t="inlineStr"/>
+      <c r="Z876" t="inlineStr"/>
+      <c r="AA876" t="n">
+        <v>0.1735999614</v>
+      </c>
+      <c r="AB876" t="n">
+        <v>63.7702186585</v>
+      </c>
+      <c r="AC876" t="n">
+        <v>8.552185538234401</v>
+      </c>
+      <c r="AD876" t="n">
+        <v>0.13049816</v>
+      </c>
+      <c r="AE876" t="n">
+        <v>1737.91676251278</v>
+      </c>
+      <c r="AF876" t="inlineStr"/>
+      <c r="AG876" t="n">
+        <v>0.0177884475</v>
+      </c>
+      <c r="AH876" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH876"/>
+  <dimension ref="A1:AH877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66213,7 +66213,7 @@
         <v>0.11637301</v>
       </c>
       <c r="AE853" t="n">
-        <v>1816.980927733444</v>
+        <v>1816.980927733443</v>
       </c>
       <c r="AF853" t="inlineStr"/>
       <c r="AG853" t="n">
@@ -66895,7 +66895,7 @@
         <v>0.140203505</v>
       </c>
       <c r="AE864" t="n">
-        <v>1777.878355524669</v>
+        <v>1777.87835552467</v>
       </c>
       <c r="AF864" t="inlineStr"/>
       <c r="AG864" t="n">
@@ -66957,7 +66957,7 @@
         <v>0.13952003</v>
       </c>
       <c r="AE865" t="n">
-        <v>1795.018439202818</v>
+        <v>1795.018439202817</v>
       </c>
       <c r="AF865" t="inlineStr"/>
       <c r="AG865" t="n">
@@ -67453,7 +67453,7 @@
         <v>0.123526715</v>
       </c>
       <c r="AE873" t="n">
-        <v>1742.016494967933</v>
+        <v>1742.016494967934</v>
       </c>
       <c r="AF873" t="inlineStr"/>
       <c r="AG873" t="n">
@@ -67647,6 +67647,68 @@
       </c>
       <c r="AH876" t="inlineStr"/>
     </row>
+    <row r="877">
+      <c r="A877" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B877" t="n">
+        <v>121.632374</v>
+      </c>
+      <c r="C877" t="n">
+        <v>0.08895462950000001</v>
+      </c>
+      <c r="D877" t="inlineStr"/>
+      <c r="E877" t="inlineStr"/>
+      <c r="F877" t="inlineStr"/>
+      <c r="G877" t="inlineStr"/>
+      <c r="H877" t="inlineStr"/>
+      <c r="I877" t="n">
+        <v>0.046862256</v>
+      </c>
+      <c r="J877" t="inlineStr"/>
+      <c r="K877" t="n">
+        <v>1534.874514051093</v>
+      </c>
+      <c r="L877" t="inlineStr"/>
+      <c r="M877" t="inlineStr"/>
+      <c r="N877" t="inlineStr"/>
+      <c r="O877" t="n">
+        <v>0.6179677246999999</v>
+      </c>
+      <c r="P877" t="inlineStr"/>
+      <c r="Q877" t="n">
+        <v>9.408e-07</v>
+      </c>
+      <c r="R877" t="inlineStr"/>
+      <c r="S877" t="inlineStr"/>
+      <c r="T877" t="inlineStr"/>
+      <c r="U877" t="inlineStr"/>
+      <c r="V877" t="inlineStr"/>
+      <c r="W877" t="inlineStr"/>
+      <c r="X877" t="inlineStr"/>
+      <c r="Y877" t="inlineStr"/>
+      <c r="Z877" t="inlineStr"/>
+      <c r="AA877" t="n">
+        <v>0.1736225073</v>
+      </c>
+      <c r="AB877" t="n">
+        <v>58.2987339975</v>
+      </c>
+      <c r="AC877" t="n">
+        <v>7.9559547381832</v>
+      </c>
+      <c r="AD877" t="n">
+        <v>0.12102064</v>
+      </c>
+      <c r="AE877" t="n">
+        <v>1723.826806144076</v>
+      </c>
+      <c r="AF877" t="inlineStr"/>
+      <c r="AG877" t="n">
+        <v>0.016800659</v>
+      </c>
+      <c r="AH877" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH877"/>
+  <dimension ref="A1:AH878"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66957,7 +66957,7 @@
         <v>0.13952003</v>
       </c>
       <c r="AE865" t="n">
-        <v>1795.018439202817</v>
+        <v>1795.018439202818</v>
       </c>
       <c r="AF865" t="inlineStr"/>
       <c r="AG865" t="n">
@@ -67515,7 +67515,7 @@
         <v>0.125987225</v>
       </c>
       <c r="AE874" t="n">
-        <v>1740.35699712395</v>
+        <v>1740.356997123951</v>
       </c>
       <c r="AF874" t="inlineStr"/>
       <c r="AG874" t="n">
@@ -67709,6 +67709,68 @@
       </c>
       <c r="AH877" t="inlineStr"/>
     </row>
+    <row r="878">
+      <c r="A878" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B878" t="n">
+        <v>123.59246076</v>
+      </c>
+      <c r="C878" t="n">
+        <v>0.0908004825</v>
+      </c>
+      <c r="D878" t="inlineStr"/>
+      <c r="E878" t="inlineStr"/>
+      <c r="F878" t="inlineStr"/>
+      <c r="G878" t="inlineStr"/>
+      <c r="H878" t="inlineStr"/>
+      <c r="I878" t="n">
+        <v>0.04733637299999999</v>
+      </c>
+      <c r="J878" t="inlineStr"/>
+      <c r="K878" t="n">
+        <v>1526.945961410902</v>
+      </c>
+      <c r="L878" t="inlineStr"/>
+      <c r="M878" t="inlineStr"/>
+      <c r="N878" t="inlineStr"/>
+      <c r="O878" t="n">
+        <v>0.6253960524</v>
+      </c>
+      <c r="P878" t="inlineStr"/>
+      <c r="Q878" t="n">
+        <v>1.008e-06</v>
+      </c>
+      <c r="R878" t="inlineStr"/>
+      <c r="S878" t="inlineStr"/>
+      <c r="T878" t="inlineStr"/>
+      <c r="U878" t="inlineStr"/>
+      <c r="V878" t="inlineStr"/>
+      <c r="W878" t="inlineStr"/>
+      <c r="X878" t="inlineStr"/>
+      <c r="Y878" t="inlineStr"/>
+      <c r="Z878" t="inlineStr"/>
+      <c r="AA878" t="n">
+        <v>0.1735600725</v>
+      </c>
+      <c r="AB878" t="n">
+        <v>60.8741379515</v>
+      </c>
+      <c r="AC878" t="n">
+        <v>7.900058100678399</v>
+      </c>
+      <c r="AD878" t="n">
+        <v>0.12493923</v>
+      </c>
+      <c r="AE878" t="n">
+        <v>1720.39148786998</v>
+      </c>
+      <c r="AF878" t="inlineStr"/>
+      <c r="AG878" t="n">
+        <v>0.0168364285</v>
+      </c>
+      <c r="AH878" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH878"/>
+  <dimension ref="A1:AH879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67453,7 +67453,7 @@
         <v>0.123526715</v>
       </c>
       <c r="AE873" t="n">
-        <v>1742.016494967934</v>
+        <v>1742.016494967933</v>
       </c>
       <c r="AF873" t="inlineStr"/>
       <c r="AG873" t="n">
@@ -67763,13 +67763,75 @@
         <v>0.12493923</v>
       </c>
       <c r="AE878" t="n">
-        <v>1720.39148786998</v>
+        <v>1720.391487869981</v>
       </c>
       <c r="AF878" t="inlineStr"/>
       <c r="AG878" t="n">
         <v>0.0168364285</v>
       </c>
       <c r="AH878" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B879" t="n">
+        <v>121.3827341404</v>
+      </c>
+      <c r="C879" t="n">
+        <v>0.08802516000000001</v>
+      </c>
+      <c r="D879" t="inlineStr"/>
+      <c r="E879" t="inlineStr"/>
+      <c r="F879" t="inlineStr"/>
+      <c r="G879" t="inlineStr"/>
+      <c r="H879" t="inlineStr"/>
+      <c r="I879" t="n">
+        <v>0.046210899</v>
+      </c>
+      <c r="J879" t="inlineStr"/>
+      <c r="K879" t="n">
+        <v>1550.731619331475</v>
+      </c>
+      <c r="L879" t="inlineStr"/>
+      <c r="M879" t="inlineStr"/>
+      <c r="N879" t="inlineStr"/>
+      <c r="O879" t="n">
+        <v>0.6159862751999999</v>
+      </c>
+      <c r="P879" t="inlineStr"/>
+      <c r="Q879" t="n">
+        <v>9.791999999999999e-07</v>
+      </c>
+      <c r="R879" t="inlineStr"/>
+      <c r="S879" t="inlineStr"/>
+      <c r="T879" t="inlineStr"/>
+      <c r="U879" t="inlineStr"/>
+      <c r="V879" t="inlineStr"/>
+      <c r="W879" t="inlineStr"/>
+      <c r="X879" t="inlineStr"/>
+      <c r="Y879" t="inlineStr"/>
+      <c r="Z879" t="inlineStr"/>
+      <c r="AA879" t="n">
+        <v>0.1736225073</v>
+      </c>
+      <c r="AB879" t="n">
+        <v>57.31822236799999</v>
+      </c>
+      <c r="AC879" t="n">
+        <v>7.6019427006528</v>
+      </c>
+      <c r="AD879" t="n">
+        <v>0.12238759</v>
+      </c>
+      <c r="AE879" t="n">
+        <v>1738.097062843228</v>
+      </c>
+      <c r="AF879" t="inlineStr"/>
+      <c r="AG879" t="n">
+        <v>0.016310892</v>
+      </c>
+      <c r="AH879" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH879"/>
+  <dimension ref="A1:AH880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67453,7 +67453,7 @@
         <v>0.123526715</v>
       </c>
       <c r="AE873" t="n">
-        <v>1742.016494967933</v>
+        <v>1742.016494967934</v>
       </c>
       <c r="AF873" t="inlineStr"/>
       <c r="AG873" t="n">
@@ -67515,7 +67515,7 @@
         <v>0.125987225</v>
       </c>
       <c r="AE874" t="n">
-        <v>1740.356997123951</v>
+        <v>1740.35699712395</v>
       </c>
       <c r="AF874" t="inlineStr"/>
       <c r="AG874" t="n">
@@ -67763,7 +67763,7 @@
         <v>0.12493923</v>
       </c>
       <c r="AE878" t="n">
-        <v>1720.391487869981</v>
+        <v>1720.39148786998</v>
       </c>
       <c r="AF878" t="inlineStr"/>
       <c r="AG878" t="n">
@@ -67833,6 +67833,68 @@
       </c>
       <c r="AH879" t="inlineStr"/>
     </row>
+    <row r="880">
+      <c r="A880" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B880" t="n">
+        <v>122.2207418172</v>
+      </c>
+      <c r="C880" t="n">
+        <v>0.088769608</v>
+      </c>
+      <c r="D880" t="inlineStr"/>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="inlineStr"/>
+      <c r="G880" t="inlineStr"/>
+      <c r="H880" t="inlineStr"/>
+      <c r="I880" t="n">
+        <v>0.046720464</v>
+      </c>
+      <c r="J880" t="inlineStr"/>
+      <c r="K880" t="n">
+        <v>1551.198004780898</v>
+      </c>
+      <c r="L880" t="inlineStr"/>
+      <c r="M880" t="inlineStr"/>
+      <c r="N880" t="inlineStr"/>
+      <c r="O880" t="n">
+        <v>0.6152274221999999</v>
+      </c>
+      <c r="P880" t="inlineStr"/>
+      <c r="Q880" t="n">
+        <v>9.815999999999998e-07</v>
+      </c>
+      <c r="R880" t="inlineStr"/>
+      <c r="S880" t="inlineStr"/>
+      <c r="T880" t="inlineStr"/>
+      <c r="U880" t="inlineStr"/>
+      <c r="V880" t="inlineStr"/>
+      <c r="W880" t="inlineStr"/>
+      <c r="X880" t="inlineStr"/>
+      <c r="Y880" t="inlineStr"/>
+      <c r="Z880" t="inlineStr"/>
+      <c r="AA880" t="n">
+        <v>0.1736121015</v>
+      </c>
+      <c r="AB880" t="n">
+        <v>61.00850251</v>
+      </c>
+      <c r="AC880" t="n">
+        <v>7.732368188164</v>
+      </c>
+      <c r="AD880" t="n">
+        <v>0.12676183</v>
+      </c>
+      <c r="AE880" t="n">
+        <v>1743.227510362562</v>
+      </c>
+      <c r="AF880" t="inlineStr"/>
+      <c r="AG880" t="n">
+        <v>0.016800659</v>
+      </c>
+      <c r="AH880" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH880"/>
+  <dimension ref="A1:AH881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66895,7 +66895,7 @@
         <v>0.140203505</v>
       </c>
       <c r="AE864" t="n">
-        <v>1777.87835552467</v>
+        <v>1777.878355524669</v>
       </c>
       <c r="AF864" t="inlineStr"/>
       <c r="AG864" t="n">
@@ -67515,7 +67515,7 @@
         <v>0.125987225</v>
       </c>
       <c r="AE874" t="n">
-        <v>1740.35699712395</v>
+        <v>1740.356997123951</v>
       </c>
       <c r="AF874" t="inlineStr"/>
       <c r="AG874" t="n">
@@ -67895,6 +67895,68 @@
       </c>
       <c r="AH880" t="inlineStr"/>
     </row>
+    <row r="881">
+      <c r="A881" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B881" t="n">
+        <v>121.2841056656</v>
+      </c>
+      <c r="C881" t="n">
+        <v>0.08809567900000001</v>
+      </c>
+      <c r="D881" t="inlineStr"/>
+      <c r="E881" t="inlineStr"/>
+      <c r="F881" t="inlineStr"/>
+      <c r="G881" t="inlineStr"/>
+      <c r="H881" t="inlineStr"/>
+      <c r="I881" t="n">
+        <v>0.046281795</v>
+      </c>
+      <c r="J881" t="inlineStr"/>
+      <c r="K881" t="n">
+        <v>1564.723182814165</v>
+      </c>
+      <c r="L881" t="inlineStr"/>
+      <c r="M881" t="inlineStr"/>
+      <c r="N881" t="inlineStr"/>
+      <c r="O881" t="n">
+        <v>0.6084146086</v>
+      </c>
+      <c r="P881" t="inlineStr"/>
+      <c r="Q881" t="n">
+        <v>9.672e-07</v>
+      </c>
+      <c r="R881" t="inlineStr"/>
+      <c r="S881" t="inlineStr"/>
+      <c r="T881" t="inlineStr"/>
+      <c r="U881" t="inlineStr"/>
+      <c r="V881" t="inlineStr"/>
+      <c r="W881" t="inlineStr"/>
+      <c r="X881" t="inlineStr"/>
+      <c r="Y881" t="inlineStr"/>
+      <c r="Z881" t="inlineStr"/>
+      <c r="AA881" t="n">
+        <v>0.1736467875</v>
+      </c>
+      <c r="AB881" t="n">
+        <v>57.38365640949999</v>
+      </c>
+      <c r="AC881" t="n">
+        <v>7.713735975662399</v>
+      </c>
+      <c r="AD881" t="n">
+        <v>0.12639731</v>
+      </c>
+      <c r="AE881" t="n">
+        <v>1752.163955473227</v>
+      </c>
+      <c r="AF881" t="inlineStr"/>
+      <c r="AG881" t="n">
+        <v>0.016437461</v>
+      </c>
+      <c r="AH881" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH881"/>
+  <dimension ref="A1:AH882"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66213,7 +66213,7 @@
         <v>0.11637301</v>
       </c>
       <c r="AE853" t="n">
-        <v>1816.980927733443</v>
+        <v>1816.980927733444</v>
       </c>
       <c r="AF853" t="inlineStr"/>
       <c r="AG853" t="n">
@@ -66895,7 +66895,7 @@
         <v>0.140203505</v>
       </c>
       <c r="AE864" t="n">
-        <v>1777.878355524669</v>
+        <v>1777.87835552467</v>
       </c>
       <c r="AF864" t="inlineStr"/>
       <c r="AG864" t="n">
@@ -67453,7 +67453,7 @@
         <v>0.123526715</v>
       </c>
       <c r="AE873" t="n">
-        <v>1742.016494967934</v>
+        <v>1742.016494967933</v>
       </c>
       <c r="AF873" t="inlineStr"/>
       <c r="AG873" t="n">
@@ -67515,7 +67515,7 @@
         <v>0.125987225</v>
       </c>
       <c r="AE874" t="n">
-        <v>1740.356997123951</v>
+        <v>1740.35699712395</v>
       </c>
       <c r="AF874" t="inlineStr"/>
       <c r="AG874" t="n">
@@ -67763,7 +67763,7 @@
         <v>0.12493923</v>
       </c>
       <c r="AE878" t="n">
-        <v>1720.39148786998</v>
+        <v>1720.391487869981</v>
       </c>
       <c r="AF878" t="inlineStr"/>
       <c r="AG878" t="n">
@@ -67957,6 +67957,68 @@
       </c>
       <c r="AH881" t="inlineStr"/>
     </row>
+    <row r="882">
+      <c r="A882" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B882" t="n">
+        <v>121.0989450816</v>
+      </c>
+      <c r="C882" t="n">
+        <v>0.08734250700000001</v>
+      </c>
+      <c r="D882" t="inlineStr"/>
+      <c r="E882" t="inlineStr"/>
+      <c r="F882" t="inlineStr"/>
+      <c r="G882" t="inlineStr"/>
+      <c r="H882" t="inlineStr"/>
+      <c r="I882" t="n">
+        <v>0.045847557</v>
+      </c>
+      <c r="J882" t="inlineStr"/>
+      <c r="K882" t="n">
+        <v>1556.328244724551</v>
+      </c>
+      <c r="L882" t="inlineStr"/>
+      <c r="M882" t="inlineStr"/>
+      <c r="N882" t="inlineStr"/>
+      <c r="O882" t="n">
+        <v>0.6054129234</v>
+      </c>
+      <c r="P882" t="inlineStr"/>
+      <c r="Q882" t="n">
+        <v>9.312e-07</v>
+      </c>
+      <c r="R882" t="inlineStr"/>
+      <c r="S882" t="inlineStr"/>
+      <c r="T882" t="inlineStr"/>
+      <c r="U882" t="inlineStr"/>
+      <c r="V882" t="inlineStr"/>
+      <c r="W882" t="inlineStr"/>
+      <c r="X882" t="inlineStr"/>
+      <c r="Y882" t="inlineStr"/>
+      <c r="Z882" t="inlineStr"/>
+      <c r="AA882" t="n">
+        <v>0.1736277102</v>
+      </c>
+      <c r="AB882" t="n">
+        <v>56.31023843099999</v>
+      </c>
+      <c r="AC882" t="n">
+        <v>7.2292984506208</v>
+      </c>
+      <c r="AD882" t="n">
+        <v>0.125531575</v>
+      </c>
+      <c r="AE882" t="n">
+        <v>1742.020679717572</v>
+      </c>
+      <c r="AF882" t="inlineStr"/>
+      <c r="AG882" t="n">
+        <v>0.016189826</v>
+      </c>
+      <c r="AH882" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH882"/>
+  <dimension ref="A1:AH883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67763,7 +67763,7 @@
         <v>0.12493923</v>
       </c>
       <c r="AE878" t="n">
-        <v>1720.391487869981</v>
+        <v>1720.39148786998</v>
       </c>
       <c r="AF878" t="inlineStr"/>
       <c r="AG878" t="n">
@@ -68019,6 +68019,68 @@
       </c>
       <c r="AH882" t="inlineStr"/>
     </row>
+    <row r="883">
+      <c r="A883" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B883" t="n">
+        <v>122.02766064</v>
+      </c>
+      <c r="C883" t="n">
+        <v>0.08761476850000001</v>
+      </c>
+      <c r="D883" t="inlineStr"/>
+      <c r="E883" t="inlineStr"/>
+      <c r="F883" t="inlineStr"/>
+      <c r="G883" t="inlineStr"/>
+      <c r="H883" t="inlineStr"/>
+      <c r="I883" t="n">
+        <v>0.046131141</v>
+      </c>
+      <c r="J883" t="inlineStr"/>
+      <c r="K883" t="n">
+        <v>1551.664390230321</v>
+      </c>
+      <c r="L883" t="inlineStr"/>
+      <c r="M883" t="inlineStr"/>
+      <c r="N883" t="inlineStr"/>
+      <c r="O883" t="n">
+        <v>0.6099154512</v>
+      </c>
+      <c r="P883" t="inlineStr"/>
+      <c r="Q883" t="n">
+        <v>9.623999999999999e-07</v>
+      </c>
+      <c r="R883" t="inlineStr"/>
+      <c r="S883" t="inlineStr"/>
+      <c r="T883" t="inlineStr"/>
+      <c r="U883" t="inlineStr"/>
+      <c r="V883" t="inlineStr"/>
+      <c r="W883" t="inlineStr"/>
+      <c r="X883" t="inlineStr"/>
+      <c r="Y883" t="inlineStr"/>
+      <c r="Z883" t="inlineStr"/>
+      <c r="AA883" t="n">
+        <v>0.1736242416</v>
+      </c>
+      <c r="AB883" t="n">
+        <v>56.482065227</v>
+      </c>
+      <c r="AC883" t="n">
+        <v>7.471517213141599</v>
+      </c>
+      <c r="AD883" t="n">
+        <v>0.12585053</v>
+      </c>
+      <c r="AE883" t="n">
+        <v>1738.705037273163</v>
+      </c>
+      <c r="AF883" t="inlineStr"/>
+      <c r="AG883" t="n">
+        <v>0.016266868</v>
+      </c>
+      <c r="AH883" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH883"/>
+  <dimension ref="A1:AH884"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67949,7 +67949,7 @@
         <v>0.12639731</v>
       </c>
       <c r="AE881" t="n">
-        <v>1752.163955473227</v>
+        <v>1752.163955473228</v>
       </c>
       <c r="AF881" t="inlineStr"/>
       <c r="AG881" t="n">
@@ -68081,6 +68081,68 @@
       </c>
       <c r="AH883" t="inlineStr"/>
     </row>
+    <row r="884">
+      <c r="A884" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B884" t="n">
+        <v>121.763739936</v>
+      </c>
+      <c r="C884" t="n">
+        <v>0.08753116350000001</v>
+      </c>
+      <c r="D884" t="inlineStr"/>
+      <c r="E884" t="inlineStr"/>
+      <c r="F884" t="inlineStr"/>
+      <c r="G884" t="inlineStr"/>
+      <c r="H884" t="inlineStr"/>
+      <c r="I884" t="n">
+        <v>0.046560948</v>
+      </c>
+      <c r="J884" t="inlineStr"/>
+      <c r="K884" t="n">
+        <v>1549.332462983206</v>
+      </c>
+      <c r="L884" t="inlineStr"/>
+      <c r="M884" t="inlineStr"/>
+      <c r="N884" t="inlineStr"/>
+      <c r="O884" t="n">
+        <v>0.6173100521</v>
+      </c>
+      <c r="P884" t="inlineStr"/>
+      <c r="Q884" t="n">
+        <v>9.984e-07</v>
+      </c>
+      <c r="R884" t="inlineStr"/>
+      <c r="S884" t="inlineStr"/>
+      <c r="T884" t="inlineStr"/>
+      <c r="U884" t="inlineStr"/>
+      <c r="V884" t="inlineStr"/>
+      <c r="W884" t="inlineStr"/>
+      <c r="X884" t="inlineStr"/>
+      <c r="Y884" t="inlineStr"/>
+      <c r="Z884" t="inlineStr"/>
+      <c r="AA884" t="n">
+        <v>0.1736138358</v>
+      </c>
+      <c r="AB884" t="n">
+        <v>57.5544842125</v>
+      </c>
+      <c r="AC884" t="n">
+        <v>7.2851950881256</v>
+      </c>
+      <c r="AD884" t="n">
+        <v>0.127900955</v>
+      </c>
+      <c r="AE884" t="n">
+        <v>1737.005234882132</v>
+      </c>
+      <c r="AF884" t="inlineStr"/>
+      <c r="AG884" t="n">
+        <v>0.0164347095</v>
+      </c>
+      <c r="AH884" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH884"/>
+  <dimension ref="A1:AH887"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67453,7 +67453,7 @@
         <v>0.123526715</v>
       </c>
       <c r="AE873" t="n">
-        <v>1742.016494967933</v>
+        <v>1742.016494967934</v>
       </c>
       <c r="AF873" t="inlineStr"/>
       <c r="AG873" t="n">
@@ -68143,6 +68143,192 @@
       </c>
       <c r="AH884" t="inlineStr"/>
     </row>
+    <row r="885">
+      <c r="A885" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B885" t="n">
+        <v>123.383152026</v>
+      </c>
+      <c r="C885" t="n">
+        <v>0.08902842</v>
+      </c>
+      <c r="D885" t="inlineStr"/>
+      <c r="E885" t="inlineStr"/>
+      <c r="F885" t="inlineStr"/>
+      <c r="G885" t="inlineStr"/>
+      <c r="H885" t="inlineStr"/>
+      <c r="I885" t="n">
+        <v>0.047207874</v>
+      </c>
+      <c r="J885" t="inlineStr"/>
+      <c r="K885" t="n">
+        <v>1545.601379387822</v>
+      </c>
+      <c r="L885" t="inlineStr"/>
+      <c r="M885" t="inlineStr"/>
+      <c r="N885" t="inlineStr"/>
+      <c r="O885" t="n">
+        <v>0.6253707573</v>
+      </c>
+      <c r="P885" t="inlineStr"/>
+      <c r="Q885" t="n">
+        <v>1.0944e-06</v>
+      </c>
+      <c r="R885" t="inlineStr"/>
+      <c r="S885" t="inlineStr"/>
+      <c r="T885" t="inlineStr"/>
+      <c r="U885" t="inlineStr"/>
+      <c r="V885" t="inlineStr"/>
+      <c r="W885" t="inlineStr"/>
+      <c r="X885" t="inlineStr"/>
+      <c r="Y885" t="inlineStr"/>
+      <c r="Z885" t="inlineStr"/>
+      <c r="AA885" t="n">
+        <v>0.1735791498</v>
+      </c>
+      <c r="AB885" t="n">
+        <v>62.795700987</v>
+      </c>
+      <c r="AC885" t="n">
+        <v>7.434252788138399</v>
+      </c>
+      <c r="AD885" t="n">
+        <v>0.12913121</v>
+      </c>
+      <c r="AE885" t="n">
+        <v>1740.29575843746</v>
+      </c>
+      <c r="AF885" t="inlineStr"/>
+      <c r="AG885" t="n">
+        <v>0.016954743</v>
+      </c>
+      <c r="AH885" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B886" t="n">
+        <v>124.9661858568</v>
+      </c>
+      <c r="C886" t="n">
+        <v>0.08992117600000002</v>
+      </c>
+      <c r="D886" t="inlineStr"/>
+      <c r="E886" t="inlineStr"/>
+      <c r="F886" t="inlineStr"/>
+      <c r="G886" t="inlineStr"/>
+      <c r="H886" t="inlineStr"/>
+      <c r="I886" t="n">
+        <v>0.047398407</v>
+      </c>
+      <c r="J886" t="inlineStr"/>
+      <c r="K886" t="n">
+        <v>1543.269452140707</v>
+      </c>
+      <c r="L886" t="inlineStr"/>
+      <c r="M886" t="inlineStr"/>
+      <c r="N886" t="inlineStr"/>
+      <c r="O886" t="n">
+        <v>0.6292662026999999</v>
+      </c>
+      <c r="P886" t="inlineStr"/>
+      <c r="Q886" t="n">
+        <v>1.1112e-06</v>
+      </c>
+      <c r="R886" t="inlineStr"/>
+      <c r="S886" t="inlineStr"/>
+      <c r="T886" t="inlineStr"/>
+      <c r="U886" t="inlineStr"/>
+      <c r="V886" t="inlineStr"/>
+      <c r="W886" t="inlineStr"/>
+      <c r="X886" t="inlineStr"/>
+      <c r="Y886" t="inlineStr"/>
+      <c r="Z886" t="inlineStr"/>
+      <c r="AA886" t="n">
+        <v>0.173551401</v>
+      </c>
+      <c r="AB886" t="n">
+        <v>65.7212519875</v>
+      </c>
+      <c r="AC886" t="n">
+        <v>7.4156205756368</v>
+      </c>
+      <c r="AD886" t="n">
+        <v>0.130452595</v>
+      </c>
+      <c r="AE886" t="n">
+        <v>1742.460045190544</v>
+      </c>
+      <c r="AF886" t="inlineStr"/>
+      <c r="AG886" t="n">
+        <v>0.016943737</v>
+      </c>
+      <c r="AH886" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B887" t="n">
+        <v>120.9875663836</v>
+      </c>
+      <c r="C887" t="n">
+        <v>0.086845239</v>
+      </c>
+      <c r="D887" t="inlineStr"/>
+      <c r="E887" t="inlineStr"/>
+      <c r="F887" t="inlineStr"/>
+      <c r="G887" t="inlineStr"/>
+      <c r="H887" t="inlineStr"/>
+      <c r="I887" t="n">
+        <v>0.045927315</v>
+      </c>
+      <c r="J887" t="inlineStr"/>
+      <c r="K887" t="n">
+        <v>1532.542586803978</v>
+      </c>
+      <c r="L887" t="inlineStr"/>
+      <c r="M887" t="inlineStr"/>
+      <c r="N887" t="inlineStr"/>
+      <c r="O887" t="n">
+        <v>0.6165933576</v>
+      </c>
+      <c r="P887" t="inlineStr"/>
+      <c r="Q887" t="n">
+        <v>1.056e-06</v>
+      </c>
+      <c r="R887" t="inlineStr"/>
+      <c r="S887" t="inlineStr"/>
+      <c r="T887" t="inlineStr"/>
+      <c r="U887" t="inlineStr"/>
+      <c r="V887" t="inlineStr"/>
+      <c r="W887" t="inlineStr"/>
+      <c r="X887" t="inlineStr"/>
+      <c r="Y887" t="inlineStr"/>
+      <c r="Z887" t="inlineStr"/>
+      <c r="AA887" t="n">
+        <v>0.1736259759</v>
+      </c>
+      <c r="AB887" t="n">
+        <v>60.8981137835</v>
+      </c>
+      <c r="AC887" t="n">
+        <v>7.3038273006272</v>
+      </c>
+      <c r="AD887" t="n">
+        <v>0.125349315</v>
+      </c>
+      <c r="AE887" t="n">
+        <v>1722.796634610705</v>
+      </c>
+      <c r="AF887" t="inlineStr"/>
+      <c r="AG887" t="n">
+        <v>0.0161980805</v>
+      </c>
+      <c r="AH887" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH887"/>
+  <dimension ref="A1:AH889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67515,7 +67515,7 @@
         <v>0.125987225</v>
       </c>
       <c r="AE874" t="n">
-        <v>1740.35699712395</v>
+        <v>1740.356997123951</v>
       </c>
       <c r="AF874" t="inlineStr"/>
       <c r="AG874" t="n">
@@ -67949,7 +67949,7 @@
         <v>0.12639731</v>
       </c>
       <c r="AE881" t="n">
-        <v>1752.163955473228</v>
+        <v>1752.163955473227</v>
       </c>
       <c r="AF881" t="inlineStr"/>
       <c r="AG881" t="n">
@@ -68329,6 +68329,130 @@
       </c>
       <c r="AH887" t="inlineStr"/>
     </row>
+    <row r="888">
+      <c r="A888" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B888" t="n">
+        <v>120.6507405572</v>
+      </c>
+      <c r="C888" t="n">
+        <v>0.08678926000000001</v>
+      </c>
+      <c r="D888" t="inlineStr"/>
+      <c r="E888" t="inlineStr"/>
+      <c r="F888" t="inlineStr"/>
+      <c r="G888" t="inlineStr"/>
+      <c r="H888" t="inlineStr"/>
+      <c r="I888" t="n">
+        <v>0.045572835</v>
+      </c>
+      <c r="J888" t="inlineStr"/>
+      <c r="K888" t="n">
+        <v>1539.538368545323</v>
+      </c>
+      <c r="L888" t="inlineStr"/>
+      <c r="M888" t="inlineStr"/>
+      <c r="N888" t="inlineStr"/>
+      <c r="O888" t="n">
+        <v>0.6236001003</v>
+      </c>
+      <c r="P888" t="inlineStr"/>
+      <c r="Q888" t="n">
+        <v>1.0968e-06</v>
+      </c>
+      <c r="R888" t="inlineStr"/>
+      <c r="S888" t="inlineStr"/>
+      <c r="T888" t="inlineStr"/>
+      <c r="U888" t="inlineStr"/>
+      <c r="V888" t="inlineStr"/>
+      <c r="W888" t="inlineStr"/>
+      <c r="X888" t="inlineStr"/>
+      <c r="Y888" t="inlineStr"/>
+      <c r="Z888" t="inlineStr"/>
+      <c r="AA888" t="n">
+        <v>0.1736259759</v>
+      </c>
+      <c r="AB888" t="n">
+        <v>59.089436957</v>
+      </c>
+      <c r="AC888" t="n">
+        <v>7.266562875623999</v>
+      </c>
+      <c r="AD888" t="n">
+        <v>0.128721125</v>
+      </c>
+      <c r="AE888" t="n">
+        <v>1727.619177168647</v>
+      </c>
+      <c r="AF888" t="inlineStr"/>
+      <c r="AG888" t="n">
+        <v>0.0157578405</v>
+      </c>
+      <c r="AH888" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B889" t="n">
+        <v>120.2030412864</v>
+      </c>
+      <c r="C889" t="n">
+        <v>0.08574310700000001</v>
+      </c>
+      <c r="D889" t="inlineStr"/>
+      <c r="E889" t="inlineStr"/>
+      <c r="F889" t="inlineStr"/>
+      <c r="G889" t="inlineStr"/>
+      <c r="H889" t="inlineStr"/>
+      <c r="I889" t="n">
+        <v>0.045364578</v>
+      </c>
+      <c r="J889" t="inlineStr"/>
+      <c r="K889" t="n">
+        <v>1535.807284949939</v>
+      </c>
+      <c r="L889" t="inlineStr"/>
+      <c r="M889" t="inlineStr"/>
+      <c r="N889" t="inlineStr"/>
+      <c r="O889" t="n">
+        <v>0.6239458</v>
+      </c>
+      <c r="P889" t="inlineStr"/>
+      <c r="Q889" t="n">
+        <v>1.0824e-06</v>
+      </c>
+      <c r="R889" t="inlineStr"/>
+      <c r="S889" t="inlineStr"/>
+      <c r="T889" t="inlineStr"/>
+      <c r="U889" t="inlineStr"/>
+      <c r="V889" t="inlineStr"/>
+      <c r="W889" t="inlineStr"/>
+      <c r="X889" t="inlineStr"/>
+      <c r="Y889" t="inlineStr"/>
+      <c r="Z889" t="inlineStr"/>
+      <c r="AA889" t="n">
+        <v>0.1736329131</v>
+      </c>
+      <c r="AB889" t="n">
+        <v>60.33917719999999</v>
+      </c>
+      <c r="AC889" t="n">
+        <v>7.1547696006144</v>
+      </c>
+      <c r="AD889" t="n">
+        <v>0.12657957</v>
+      </c>
+      <c r="AE889" t="n">
+        <v>1724.575237394953</v>
+      </c>
+      <c r="AF889" t="inlineStr"/>
+      <c r="AG889" t="n">
+        <v>0.0156973075</v>
+      </c>
+      <c r="AH889" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH889"/>
+  <dimension ref="A1:AH891"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66895,7 +66895,7 @@
         <v>0.140203505</v>
       </c>
       <c r="AE864" t="n">
-        <v>1777.87835552467</v>
+        <v>1777.878355524669</v>
       </c>
       <c r="AF864" t="inlineStr"/>
       <c r="AG864" t="n">
@@ -67763,7 +67763,7 @@
         <v>0.12493923</v>
       </c>
       <c r="AE878" t="n">
-        <v>1720.39148786998</v>
+        <v>1720.391487869981</v>
       </c>
       <c r="AF878" t="inlineStr"/>
       <c r="AG878" t="n">
@@ -68453,6 +68453,130 @@
       </c>
       <c r="AH889" t="inlineStr"/>
     </row>
+    <row r="890">
+      <c r="A890" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B890" t="n">
+        <v>119.1121839036</v>
+      </c>
+      <c r="C890" t="n">
+        <v>0.0846907745</v>
+      </c>
+      <c r="D890" t="inlineStr"/>
+      <c r="E890" t="inlineStr"/>
+      <c r="F890" t="inlineStr"/>
+      <c r="G890" t="inlineStr"/>
+      <c r="H890" t="inlineStr"/>
+      <c r="I890" t="n">
+        <v>0.04493034</v>
+      </c>
+      <c r="J890" t="inlineStr"/>
+      <c r="K890" t="n">
+        <v>1540.937524893592</v>
+      </c>
+      <c r="L890" t="inlineStr"/>
+      <c r="M890" t="inlineStr"/>
+      <c r="N890" t="inlineStr"/>
+      <c r="O890" t="n">
+        <v>0.6228412473</v>
+      </c>
+      <c r="P890" t="inlineStr"/>
+      <c r="Q890" t="n">
+        <v>1.0272e-06</v>
+      </c>
+      <c r="R890" t="inlineStr"/>
+      <c r="S890" t="inlineStr"/>
+      <c r="T890" t="inlineStr"/>
+      <c r="U890" t="inlineStr"/>
+      <c r="V890" t="inlineStr"/>
+      <c r="W890" t="inlineStr"/>
+      <c r="X890" t="inlineStr"/>
+      <c r="Y890" t="inlineStr"/>
+      <c r="Z890" t="inlineStr"/>
+      <c r="AA890" t="n">
+        <v>0.1736259759</v>
+      </c>
+      <c r="AB890" t="n">
+        <v>60.626887184</v>
+      </c>
+      <c r="AC890" t="n">
+        <v>7.005711900601599</v>
+      </c>
+      <c r="AD890" t="n">
+        <v>0.127080785</v>
+      </c>
+      <c r="AE890" t="n">
+        <v>1728.751092794193</v>
+      </c>
+      <c r="AF890" t="inlineStr"/>
+      <c r="AG890" t="n">
+        <v>0.0156147625</v>
+      </c>
+      <c r="AH890" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B891" t="n">
+        <v>119.1069381824</v>
+      </c>
+      <c r="C891" t="n">
+        <v>0.08449739250000002</v>
+      </c>
+      <c r="D891" t="inlineStr"/>
+      <c r="E891" t="inlineStr"/>
+      <c r="F891" t="inlineStr"/>
+      <c r="G891" t="inlineStr"/>
+      <c r="H891" t="inlineStr"/>
+      <c r="I891" t="n">
+        <v>0.044730945</v>
+      </c>
+      <c r="J891" t="inlineStr"/>
+      <c r="K891" t="n">
+        <v>1536.740055848785</v>
+      </c>
+      <c r="L891" t="inlineStr"/>
+      <c r="M891" t="inlineStr"/>
+      <c r="N891" t="inlineStr"/>
+      <c r="O891" t="n">
+        <v>0.6263741295999999</v>
+      </c>
+      <c r="P891" t="inlineStr"/>
+      <c r="Q891" t="n">
+        <v>1.0368e-06</v>
+      </c>
+      <c r="R891" t="inlineStr"/>
+      <c r="S891" t="inlineStr"/>
+      <c r="T891" t="inlineStr"/>
+      <c r="U891" t="inlineStr"/>
+      <c r="V891" t="inlineStr"/>
+      <c r="W891" t="inlineStr"/>
+      <c r="X891" t="inlineStr"/>
+      <c r="Y891" t="inlineStr"/>
+      <c r="Z891" t="inlineStr"/>
+      <c r="AA891" t="n">
+        <v>0.1736693334</v>
+      </c>
+      <c r="AB891" t="n">
+        <v>61.600905359</v>
+      </c>
+      <c r="AC891" t="n">
+        <v>6.9311830505952</v>
+      </c>
+      <c r="AD891" t="n">
+        <v>0.12812878</v>
+      </c>
+      <c r="AE891" t="n">
+        <v>1725.45211532958</v>
+      </c>
+      <c r="AF891" t="inlineStr"/>
+      <c r="AG891" t="n">
+        <v>0.0156312715</v>
+      </c>
+      <c r="AH891" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH891"/>
+  <dimension ref="A1:AH892"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68445,7 +68445,7 @@
         <v>0.12657957</v>
       </c>
       <c r="AE889" t="n">
-        <v>1724.575237394953</v>
+        <v>1724.575237394954</v>
       </c>
       <c r="AF889" t="inlineStr"/>
       <c r="AG889" t="n">
@@ -68577,6 +68577,68 @@
       </c>
       <c r="AH891" t="inlineStr"/>
     </row>
+    <row r="892">
+      <c r="A892" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B892" t="n">
+        <v>120.2351546108</v>
+      </c>
+      <c r="C892" t="n">
+        <v>0.08543558600000001</v>
+      </c>
+      <c r="D892" t="inlineStr"/>
+      <c r="E892" t="inlineStr"/>
+      <c r="F892" t="inlineStr"/>
+      <c r="G892" t="inlineStr"/>
+      <c r="H892" t="inlineStr"/>
+      <c r="I892" t="n">
+        <v>0.044908185</v>
+      </c>
+      <c r="J892" t="inlineStr"/>
+      <c r="K892" t="n">
+        <v>1546.067764837245</v>
+      </c>
+      <c r="L892" t="inlineStr"/>
+      <c r="M892" t="inlineStr"/>
+      <c r="N892" t="inlineStr"/>
+      <c r="O892" t="n">
+        <v>0.6281110598</v>
+      </c>
+      <c r="P892" t="inlineStr"/>
+      <c r="Q892" t="n">
+        <v>1.104e-06</v>
+      </c>
+      <c r="R892" t="inlineStr"/>
+      <c r="S892" t="inlineStr"/>
+      <c r="T892" t="inlineStr"/>
+      <c r="U892" t="inlineStr"/>
+      <c r="V892" t="inlineStr"/>
+      <c r="W892" t="inlineStr"/>
+      <c r="X892" t="inlineStr"/>
+      <c r="Y892" t="inlineStr"/>
+      <c r="Z892" t="inlineStr"/>
+      <c r="AA892" t="n">
+        <v>0.1736121015</v>
+      </c>
+      <c r="AB892" t="n">
+        <v>65.41406164</v>
+      </c>
+      <c r="AC892" t="n">
+        <v>6.893918625592</v>
+      </c>
+      <c r="AD892" t="n">
+        <v>0.134917965</v>
+      </c>
+      <c r="AE892" t="n">
+        <v>1739.693627046437</v>
+      </c>
+      <c r="AF892" t="inlineStr"/>
+      <c r="AG892" t="n">
+        <v>0.0157413315</v>
+      </c>
+      <c r="AH892" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BinancePTF/Positions.xlsx
+++ b/BinancePTF/Positions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH892"/>
+  <dimension ref="A1:AH893"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66895,7 +66895,7 @@
         <v>0.140203505</v>
       </c>
       <c r="AE864" t="n">
-        <v>1777.878355524669</v>
+        <v>1777.87835552467</v>
       </c>
       <c r="AF864" t="inlineStr"/>
       <c r="AG864" t="n">
@@ -66957,7 +66957,7 @@
         <v>0.13952003</v>
       </c>
       <c r="AE865" t="n">
-        <v>1795.018439202818</v>
+        <v>1795.018439202817</v>
       </c>
       <c r="AF865" t="inlineStr"/>
       <c r="AG865" t="n">
@@ -67949,7 +67949,7 @@
         <v>0.12639731</v>
       </c>
       <c r="AE881" t="n">
-        <v>1752.163955473227</v>
+        <v>1752.163955473228</v>
       </c>
       <c r="AF881" t="inlineStr"/>
       <c r="AG881" t="n">
@@ -68639,6 +68639,68 @@
       </c>
       <c r="AH892" t="inlineStr"/>
     </row>
+    <row r="893">
+      <c r="A893" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B893" t="n">
+        <v>120.87969474</v>
+      </c>
+      <c r="C893" t="n">
+        <v>0.085774368</v>
+      </c>
+      <c r="D893" t="inlineStr"/>
+      <c r="E893" t="inlineStr"/>
+      <c r="F893" t="inlineStr"/>
+      <c r="G893" t="inlineStr"/>
+      <c r="H893" t="inlineStr"/>
+      <c r="I893" t="n">
+        <v>0.045391164</v>
+      </c>
+      <c r="J893" t="inlineStr"/>
+      <c r="K893" t="n">
+        <v>1538.139212197054</v>
+      </c>
+      <c r="L893" t="inlineStr"/>
+      <c r="M893" t="inlineStr"/>
+      <c r="N893" t="inlineStr"/>
+      <c r="O893" t="n">
+        <v>0.6406827245</v>
+      </c>
+      <c r="P893" t="inlineStr"/>
+      <c r="Q893" t="n">
+        <v>1.2072e-06</v>
+      </c>
+      <c r="R893" t="inlineStr"/>
+      <c r="S893" t="inlineStr"/>
+      <c r="T893" t="inlineStr"/>
+      <c r="U893" t="inlineStr"/>
+      <c r="V893" t="inlineStr"/>
+      <c r="W893" t="inlineStr"/>
+      <c r="X893" t="inlineStr"/>
+      <c r="Y893" t="inlineStr"/>
+      <c r="Z893" t="inlineStr"/>
+      <c r="AA893" t="n">
+        <v>0.173586087</v>
+      </c>
+      <c r="AB893" t="n">
+        <v>65.48449064649999</v>
+      </c>
+      <c r="AC893" t="n">
+        <v>6.7821253505824</v>
+      </c>
+      <c r="AD893" t="n">
+        <v>0.13177398</v>
+      </c>
+      <c r="AE893" t="n">
+        <v>1732.379035102337</v>
+      </c>
+      <c r="AF893" t="inlineStr"/>
+      <c r="AG893" t="n">
+        <v>0.0163026375</v>
+      </c>
+      <c r="AH893" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
